--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487699_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487699_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3032</v>
+        <v>8.4315</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2042</v>
+        <v>6.9049</v>
       </c>
       <c r="F2" t="n">
-        <v>2.099</v>
+        <v>1.5266</v>
       </c>
       <c r="G2" t="n">
         <v>5.6056</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2144</v>
+        <v>-0.0861</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7874</v>
+        <v>-0.0867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.573</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.5537</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0767</v>
+        <v>4.712</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8124</v>
+        <v>5.6112</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7357</v>
+        <v>-0.8992</v>
       </c>
       <c r="G3" t="n">
         <v>6.8606</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0982</v>
+        <v>0.7335</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7608</v>
+        <v>0.5596</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3374</v>
+        <v>0.1739</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.538</v>
+        <v>4.2297</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4206</v>
+        <v>3.5047</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1174</v>
+        <v>0.725</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6901</v>
+        <v>3.8101</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2101</v>
+        <v>1.3231</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9002</v>
+        <v>2.487</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0744</v>
+        <v>3.9016</v>
       </c>
       <c r="K4" t="n">
-        <v>0.103</v>
+        <v>1.3924</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9715</v>
+        <v>2.5093</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6156</v>
+        <v>-0.0915</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3131</v>
+        <v>-0.0692</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9287</v>
+        <v>-0.0223</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.194</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>1.042</v>
+        <v>-0.2341</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3163</v>
+        <v>0.3076</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7257</v>
+        <v>-0.5417</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0563</v>
+        <v>3.4656</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6038</v>
+        <v>1.6208</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4525</v>
+        <v>1.8449</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8101</v>
+        <v>2.6901</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3231</v>
+        <v>-0.2101</v>
       </c>
       <c r="I5" t="n">
-        <v>2.487</v>
+        <v>2.9002</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9016</v>
+        <v>2.0744</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3924</v>
+        <v>0.103</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5093</v>
+        <v>1.9715</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0915</v>
+        <v>0.6156</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0692</v>
+        <v>-0.3131</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0223</v>
+        <v>0.9287</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7463</v>
+        <v>-0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4076</v>
+        <v>0.9696</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5933</v>
+        <v>0.5165</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8142</v>
+        <v>0.4531</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3443</v>
+        <v>1.9172</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6047</v>
+        <v>1.905</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2603</v>
+        <v>0.0122</v>
       </c>
       <c r="G6" t="n">
         <v>1.2989</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1335</v>
+        <v>0.7063</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2557</v>
+        <v>0.556</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1222</v>
+        <v>0.1503</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6995</v>
+        <v>0.9012</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9928</v>
+        <v>0.2826</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6923</v>
+        <v>0.6186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3314</v>
+        <v>1.1343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.421</v>
+        <v>-1.2787</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9104</v>
+        <v>2.413</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0377</v>
+        <v>1.8207</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3831</v>
+        <v>-0.8815</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6546</v>
+        <v>2.7022</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2937</v>
+        <v>-0.6863</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0379</v>
+        <v>-0.3971</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2558</v>
+        <v>-0.2892</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3284</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q7" t="n">
         <v>-3.8806</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0368</v>
+        <v>0.1237</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8501</v>
+        <v>-0.1052</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1867</v>
+        <v>0.2288</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6597</v>
+        <v>2.1657</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6597</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1827</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2179</v>
+        <v>-2.0929</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4006</v>
+        <v>2.6105</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1343</v>
+        <v>1.3314</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2787</v>
+        <v>0.421</v>
       </c>
       <c r="I8" t="n">
-        <v>2.413</v>
+        <v>0.9104</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8207</v>
+        <v>1.0377</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8815</v>
+        <v>0.3831</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7022</v>
+        <v>0.6546</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6863</v>
+        <v>0.2937</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3971</v>
+        <v>0.0379</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2892</v>
+        <v>0.2558</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5224</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q8" t="n">
         <v>-3.8806</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5949</v>
+        <v>0.8549</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6057</v>
+        <v>0.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0108</v>
+        <v>0.1049</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1657</v>
+        <v>0.6597</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4637</v>
+        <v>-1.0004</v>
       </c>
       <c r="E9" t="n">
         <v>-0.874</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5897</v>
+        <v>-0.1264</v>
       </c>
       <c r="G9" t="n">
         <v>0.6768999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7824</v>
+        <v>-0.3191</v>
       </c>
       <c r="T9" t="n">
         <v>0.0134</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7958</v>
+        <v>-0.3325</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>M. BENÍTEZ MONTESINOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6541</v>
+        <v>-1.9534</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3649</v>
+        <v>-0.9296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7108</v>
+        <v>-1.0239</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6888</v>
+        <v>-0.9833</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2778</v>
+        <v>-0.6179</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.411</v>
+        <v>-0.3654</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2029</v>
+        <v>0.0406</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4871</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2842</v>
+        <v>0.0406</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4859</v>
+        <v>-1.0239</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2092</v>
+        <v>-0.6179</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6952</v>
+        <v>-0.406</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8795</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9425</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.063</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0955</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BENÍTEZ MONTESINOS</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9534</v>
+        <v>-2.5967</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9296</v>
+        <v>-0.9687</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0239</v>
+        <v>-1.628</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9833</v>
+        <v>-2.0176</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6179</v>
+        <v>-1.1361</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3654</v>
+        <v>-0.8815</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0406</v>
+        <v>-0.4026</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.0618</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0406</v>
+        <v>-0.4643</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0239</v>
+        <v>-1.615</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6179</v>
+        <v>-1.1979</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.406</v>
+        <v>-0.4171</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.5089</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.5981</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.0891</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7241</v>
+        <v>-3.219</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0688</v>
+        <v>-3.7663</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6553</v>
+        <v>0.5473</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0176</v>
+        <v>-1.6888</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1361</v>
+        <v>-1.2778</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8815</v>
+        <v>-0.411</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4026</v>
+        <v>-1.2029</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0618</v>
+        <v>-1.4871</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4643</v>
+        <v>0.2842</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.615</v>
+        <v>-0.4859</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1979</v>
+        <v>0.2092</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4171</v>
+        <v>-0.6952</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1642</v>
+        <v>-3.1045</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3816</v>
+        <v>0.3146</v>
       </c>
       <c r="T13" t="n">
-        <v>0.498</v>
+        <v>0.5411</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1164</v>
+        <v>-0.2265</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.894</v>
+        <v>0.0955</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.894</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.452</v>
+        <v>13.4519</v>
       </c>
       <c r="E14" t="n">
         <v>10.2681</v>
       </c>
       <c r="F14" t="n">
-        <v>3.183799999999999</v>
+        <v>3.1837</v>
       </c>
       <c r="G14" t="n">
         <v>17.7349</v>
@@ -1546,13 +1546,13 @@
         <v>11.642</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5723</v>
+        <v>3.5722</v>
       </c>
       <c r="T14" t="n">
-        <v>3.650399999999999</v>
+        <v>3.6504</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07800000000000007</v>
+        <v>-0.07820000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>4.7567</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1442</v>
+        <v>1.1136</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8238</v>
+        <v>2.5235</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6797</v>
+        <v>-1.4099</v>
       </c>
       <c r="G15" t="n">
         <v>0.2533</v>
@@ -1624,13 +1624,13 @@
         <v>3.2985</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0897</v>
+        <v>-0.1203</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4149</v>
+        <v>0.1146</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5047</v>
+        <v>-0.2349</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3776</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7004</v>
+        <v>1.0736</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8362</v>
+        <v>2.2366</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1357</v>
+        <v>-1.163</v>
       </c>
       <c r="G16" t="n">
         <v>0.3178</v>
@@ -1702,13 +1702,13 @@
         <v>3.6866</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1577</v>
+        <v>-0.7846</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8109</v>
+        <v>-0.4105</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3468</v>
+        <v>-0.374</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1761</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2621</v>
+        <v>0.7443</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2549</v>
+        <v>0.6553</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0072</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1621</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5758</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3634</v>
+        <v>0.037</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V17" t="n">
         <v>1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1677</v>
+        <v>0.1718</v>
       </c>
       <c r="E18" t="n">
-        <v>4.3303</v>
+        <v>0.1577</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.498</v>
+        <v>0.0141</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5844</v>
+        <v>0.2955</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2358</v>
+        <v>0.4523</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3487</v>
+        <v>-0.1568</v>
       </c>
       <c r="J18" t="n">
-        <v>2.956</v>
+        <v>1.542</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0988</v>
+        <v>1.0092</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0548</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.5404</v>
+        <v>-1.2466</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.137</v>
+        <v>-0.5569</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.4035</v>
+        <v>-0.6896</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9719</v>
+        <v>-0.3177</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4221</v>
+        <v>-0.4142</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5498</v>
+        <v>0.0965</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4955</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1736</v>
+        <v>-0.7946</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5446</v>
+        <v>-0.0209</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7183</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3875</v>
+        <v>-2.6808</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7212</v>
+        <v>-0.0008</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6663</v>
+        <v>-2.6799</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5059</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6683</v>
+        <v>0.8692</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1624</v>
+        <v>0.0507</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8816</v>
+        <v>-3.6006</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0529</v>
+        <v>-0.87</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8286</v>
+        <v>-2.7306</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5523</v>
+        <v>2.7164</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>3.6866</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0392</v>
+        <v>-0.8303</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4282</v>
+        <v>0.0294</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3889</v>
+        <v>-0.8597</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3465</v>
+        <v>-1.414</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1426</v>
+        <v>3.3293</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2039</v>
+        <v>-4.7433</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2955</v>
+        <v>-1.5844</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4523</v>
+        <v>-1.2358</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1568</v>
+        <v>-0.3487</v>
       </c>
       <c r="J20" t="n">
-        <v>1.542</v>
+        <v>2.956</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0092</v>
+        <v>-0.0988</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5328000000000001</v>
+        <v>3.0548</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2466</v>
+        <v>-4.5404</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5569</v>
+        <v>-1.137</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6896</v>
+        <v>-3.4035</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.836</v>
+        <v>0.7256</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7145</v>
+        <v>0.4211</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1216</v>
+        <v>0.3045</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.4955</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6043</v>
+        <v>-1.7984</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.381</v>
+        <v>-1.6813</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2233</v>
+        <v>-0.117</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9742</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0182</v>
+        <v>-0.2123</v>
       </c>
       <c r="T21" t="n">
-        <v>0.498</v>
+        <v>0.1977</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5161</v>
+        <v>-0.4099</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9107</v>
+        <v>-1.8119</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9218</v>
+        <v>-1.2572</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9889</v>
+        <v>-0.5547</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6808</v>
+        <v>-3.3875</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0008</v>
+        <v>-2.7212</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6799</v>
+        <v>-0.6663</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9199000000000001</v>
+        <v>-1.5059</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8692</v>
+        <v>-1.6683</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0507</v>
+        <v>0.1624</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.6006</v>
+        <v>-1.8816</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.87</v>
+        <v>-1.0529</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7306</v>
+        <v>-0.8286</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7164</v>
+        <v>1.5523</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.6866</v>
+        <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9464</v>
+        <v>0.4009</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8715000000000001</v>
+        <v>0.6264</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0749</v>
+        <v>-0.2254</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>G. ARTILES ROMERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5369</v>
+        <v>-3.0579</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0969</v>
+        <v>-4.0485</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.44</v>
+        <v>0.9906</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3565</v>
+        <v>-4.5948</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7005</v>
+        <v>-1.7886</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.057</v>
+        <v>-2.8062</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3455</v>
+        <v>-1.1046</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6395</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2941</v>
+        <v>-1.0099</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7019</v>
+        <v>-3.4902</v>
       </c>
       <c r="N23" t="n">
-        <v>0.061</v>
+        <v>-1.6939</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7629</v>
+        <v>-1.7963</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9403</v>
+        <v>4.2687</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7028</v>
+        <v>-0.4332</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4722</v>
+        <v>-0.3155</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2306</v>
+        <v>-0.1177</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4477</v>
+        <v>0.6119</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4477</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9081</v>
+        <v>-3.2822</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5639</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6558</v>
+        <v>-2.3855</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8613</v>
+        <v>-1.3565</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6896</v>
+        <v>1.7005</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1717</v>
+        <v>-3.057</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8996</v>
+        <v>0.3455</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6055</v>
+        <v>1.6395</v>
       </c>
       <c r="L24" t="n">
         <v>-1.2941</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0383</v>
+        <v>-1.7019</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1223</v>
+        <v>-1.7629</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9706</v>
+        <v>-0.4481</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0359</v>
+        <v>-0.272</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9347</v>
+        <v>-0.1761</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2821</v>
+        <v>-2.4477</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. ARTILES ROMERO</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9109</v>
+        <v>-3.729</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1496</v>
+        <v>-4.4638</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2387</v>
+        <v>0.7348</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5948</v>
+        <v>-1.8613</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7886</v>
+        <v>-0.6896</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.8062</v>
+        <v>-1.1717</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.1046</v>
+        <v>-1.8996</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.6055</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0099</v>
+        <v>-1.2941</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.4902</v>
+        <v>0.0383</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6939</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7963</v>
+        <v>0.1223</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3582</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R25" t="n">
-        <v>4.2687</v>
+        <v>1.5523</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2862</v>
+        <v>-0.7915</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4166</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1304</v>
+        <v>-0.8557</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6119</v>
+        <v>0.2821</v>
       </c>
       <c r="W25" t="n">
         <v>0.2821</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.452</v>
+        <v>-12.7847</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.466</v>
+        <v>-3.466000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.9861</v>
+        <v>-9.318699999999998</v>
       </c>
       <c r="G26" t="n">
         <v>-17.735</v>
@@ -2461,7 +2461,7 @@
         <v>3.6088</v>
       </c>
       <c r="L26" t="n">
-        <v>2.8921</v>
+        <v>2.892099999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-24.2357</v>
@@ -2482,16 +2482,16 @@
         <v>24.254</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.572299999999999</v>
+        <v>-2.9052</v>
       </c>
       <c r="T26" t="n">
-        <v>0.07819999999999983</v>
+        <v>0.07819999999999989</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.6505</v>
+        <v>-2.9831</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.7566</v>
+        <v>-4.756600000000001</v>
       </c>
       <c r="W26" t="n">
         <v>1.597</v>
